--- a/data/processed/positivacao/2025-07_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2025-07_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26817,7 +26817,7 @@
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr"/>
@@ -38143,7 +38143,7 @@
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1455" t="inlineStr"/>
@@ -66359,7 +66359,7 @@
     <row r="2541">
       <c r="A2541" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2541" t="inlineStr"/>
@@ -67952,12 +67952,12 @@
       <c r="A2603" t="inlineStr"/>
       <c r="B2603" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 10 cliente(s), não positivou 86 cliente(s) - Total vendido: R$ 5.444,80
+          <t>Vendedor 1 - VENDEDOR 01: positivou 10 cliente(s), não positivou 86 cliente(s) - Total vendido: R$ 5.444,80
 Vendedor 18 - LOJA: positivou 280 cliente(s), não positivou 633 cliente(s) - Total vendido: R$ 75.803,37
-Vendedor 3 - FERNANDA: positivou 119 cliente(s), não positivou 316 cliente(s) - Total vendido: R$ 122.040,17
-Vendedor 4 - DANIELA: positivou 128 cliente(s), não positivou 511 cliente(s) - Total vendido: R$ 69.354,27
+Vendedor 3 - VENDEDOR 03: positivou 119 cliente(s), não positivou 316 cliente(s) - Total vendido: R$ 122.040,17
+Vendedor 4 - VENDEDOR 04: positivou 128 cliente(s), não positivou 511 cliente(s) - Total vendido: R$ 69.354,27
 Vendedor 5 - SITE: positivou 0 cliente(s), não positivou 445 cliente(s) - Total vendido: R$ 0,00
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 60 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 60 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2603" t="inlineStr"/>
